--- a/Data_Analytics/Manipulating-workbooks.xlsx
+++ b/Data_Analytics/Manipulating-workbooks.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OTAS\Desktop\Data_Science\Data_Analytics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6153CF42-44C1-4933-8B20-DCE821987CD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90ABCEA2-0669-48AE-BBED-777ED3BC3796}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E88BD08D-05DC-4E74-9C9B-2BC0226406C5}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Data_Movements" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
